--- a/DateBase/orders/Dang Nguyen48_2026-9-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-29.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>6.5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0121351010610370</v>
+        <v>0121351010610376.5</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,174 @@
         <v>6.5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>87_紫霞非洲菊_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F16" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3</v>
+      </c>
+      <c r="C17" t="str">
+        <v>516_火焰兰_Crocosmia_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>641_绿枫叶_maple leaf_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="C19" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="C20" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>318_尤加利果_Eucalyptus pods_undefined_1bunch</v>
+      </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>558_油画小菊_Helenium_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>435_猫眼_Echinacea_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>755_豌豆花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>84_堪培拉_undefined_Gerbera L._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +746,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0121351010610376.5</v>
+        <v>0121351010610376.51021064151410551055510101015100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -688,10 +688,83 @@
       <c r="C31" t="str">
         <v>84_堪培拉_undefined_Gerbera L._10stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>4</v>
+      </c>
+      <c r="C33" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>7_翠绿洋桔梗_Dark Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F37" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F38" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>5</v>
+      </c>
+      <c r="C39" t="str">
+        <v>636_干花大叶白_undefined_undefined_1stem</v>
+      </c>
+      <c r="F39" t="str">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L39"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -746,7 +819,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0121351010610376.51021064151410551055510101015100</v>
+        <v>0121351010610376.51021064151410551055510101015101010920155111130</v>
       </c>
     </row>
   </sheetData>
